--- a/internal_doc/05.测试设计/story/民生银行资源管控/Story-民生银行资源管控测试用例（资源监控-CL_GROUP_LIST_INFO）.xlsx
+++ b/internal_doc/05.测试设计/story/民生银行资源管控/Story-民生银行资源管控测试用例（资源监控-CL_GROUP_LIST_INFO）.xlsx
@@ -98,11 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
-2、检查CL中字段值跟sdb.list(7)查询的信息是否一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Groupdbpath，检查字段名、类型、字段值正确性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -126,55 +121,56 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>GroupNodeID，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupID，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupName，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PrimaryNode，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Role，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Status，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
-2、检查CL中字段值跟sdb.list(7)查询的信息是否一致，覆盖如下取值：
+2、检查CL中字段值跟db.list(7)查询的信息是否一致</t>
+  </si>
+  <si>
+    <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
+2、检查CL中字段值跟db.list(7)查询的信息是否一致，覆盖如下取值：
   0：直连服务，对应数据库参数 svcname
   1：复制服务，对应数据库参数 replname
   2：分区服务，对应数据库参数 shardname
   3：编目服务，对应数据库参数 catalogname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
-2、检查CL中字段值跟sdb.list(7)查询的信息是否一致，覆盖如下取值：
+2、检查CL中字段值跟db.list(7)查询的信息是否一致，覆盖如下取值：
   服务名为端口号
   services文件中的服务名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GroupNodeID，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GroupID，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GroupName，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PrimaryNode，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Role，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Status，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Version，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
-2、检查CL中字段值跟sdb.list(7)查询的信息是否一致，覆盖如下取值：
+2、检查CL中字段值跟db.list(7)查询的信息是否一致，覆盖如下取值：
   0：数据节点
   2：编目节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -702,10 +698,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
@@ -713,7 +709,7 @@
     </row>
     <row r="3" spans="1:9" ht="81">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
@@ -728,10 +724,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -739,7 +735,7 @@
     </row>
     <row r="4" spans="1:9" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
@@ -754,10 +750,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -765,7 +761,7 @@
     </row>
     <row r="5" spans="1:9" ht="81">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
@@ -780,10 +776,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -791,7 +787,7 @@
     </row>
     <row r="6" spans="1:9" ht="81">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
@@ -806,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -817,7 +813,7 @@
     </row>
     <row r="7" spans="1:9" ht="81">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>15</v>
@@ -832,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -843,7 +839,7 @@
     </row>
     <row r="8" spans="1:9" ht="81">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>15</v>
@@ -858,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
@@ -869,7 +865,7 @@
     </row>
     <row r="9" spans="1:9" ht="81">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
@@ -884,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="3">
         <v>1</v>
@@ -895,7 +891,7 @@
     </row>
     <row r="10" spans="1:9" ht="81">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>15</v>
@@ -913,7 +909,7 @@
         <v>34</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10" s="3">
         <v>1</v>
@@ -921,7 +917,7 @@
     </row>
     <row r="11" spans="1:9" ht="81">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>15</v>
@@ -936,10 +932,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
@@ -947,7 +943,7 @@
     </row>
     <row r="12" spans="1:9" ht="81">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>15</v>
@@ -962,10 +958,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3">
         <v>1</v>
